--- a/VerveStacks_EST/vt_EST_RSD_V1.xlsx
+++ b/VerveStacks_EST/vt_EST_RSD_V1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECF603D-B12B-4D4A-9069-B8D5B321B9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAEE1B3-9479-4408-88CF-B53158BFD56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2305,7 +2305,9 @@
       <c r="D19" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="28"/>
+      <c r="E19" s="28">
+        <v>0.25</v>
+      </c>
       <c r="G19" s="26">
         <v>1</v>
       </c>
@@ -2334,7 +2336,9 @@
       <c r="C20" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="28"/>
+      <c r="E20" s="28">
+        <v>0.25</v>
+      </c>
       <c r="F20" s="10"/>
       <c r="G20" s="11"/>
       <c r="H20" s="12"/>
@@ -2360,7 +2364,9 @@
       <c r="C21" t="s">
         <v>91</v>
       </c>
-      <c r="E21" s="28"/>
+      <c r="E21" s="28">
+        <v>0.25</v>
+      </c>
       <c r="F21" s="10"/>
       <c r="G21" s="11"/>
       <c r="H21" s="12"/>
@@ -2386,7 +2392,9 @@
       <c r="C22" t="s">
         <v>101</v>
       </c>
-      <c r="E22" s="28"/>
+      <c r="E22" s="28">
+        <v>0.25</v>
+      </c>
       <c r="F22" s="10"/>
       <c r="G22" s="11"/>
       <c r="H22" s="12"/>

--- a/VerveStacks_EST/vt_EST_RSD_V1.xlsx
+++ b/VerveStacks_EST/vt_EST_RSD_V1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAEE1B3-9479-4408-88CF-B53158BFD56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE15329-E892-40DF-A76C-D88C178F2501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_EST/vt_EST_RSD_V1.xlsx
+++ b/VerveStacks_EST/vt_EST_RSD_V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD82493-8B65-4A3D-BD67-A089E8FC0514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D479204-21BB-4484-B32F-320E7879CA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sector_Fuels_RSD" sheetId="1" r:id="rId1"/>
@@ -771,7 +771,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="99">
   <si>
     <t>Sector Name</t>
   </si>
@@ -854,12 +854,6 @@
     <t>NRG</t>
   </si>
   <si>
-    <t>DAYNITE</t>
-  </si>
-  <si>
-    <t>ELC</t>
-  </si>
-  <si>
     <t>~FI_T</t>
   </si>
   <si>
@@ -1013,9 +1007,6 @@
     <t>Residential Solar energy</t>
   </si>
   <si>
-    <t>RSDELC</t>
-  </si>
-  <si>
     <t>FTE-RSDCOA</t>
   </si>
   <si>
@@ -1050,9 +1041,6 @@
   </si>
   <si>
     <t>Sector Fuel Technology Existing Residential Solar energy</t>
-  </si>
-  <si>
-    <t>FTE-RSDELC</t>
   </si>
   <si>
     <t>twh</t>
@@ -1796,29 +1784,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:R36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.453125" customWidth="1"/>
-    <col min="11" max="11" width="7.1796875" customWidth="1"/>
-    <col min="12" max="12" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="63" customWidth="1"/>
-    <col min="14" max="14" width="6.1796875" customWidth="1"/>
-    <col min="15" max="15" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.1796875" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1839,21 +1827,21 @@
       </c>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="2:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>7</v>
@@ -1871,7 +1859,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="J3" s="7" t="s">
         <v>9</v>
       </c>
@@ -1900,7 +1888,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="22" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -1934,7 +1922,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="11"/>
@@ -1944,20 +1932,20 @@
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O5" s="13"/>
       <c r="P5" s="13"/>
       <c r="Q5" s="13"/>
       <c r="R5" s="13"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="11"/>
@@ -1965,20 +1953,20 @@
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
       <c r="L6" s="13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O6" s="13"/>
       <c r="P6" s="13"/>
       <c r="Q6" s="13"/>
       <c r="R6" s="13"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
@@ -1986,20 +1974,20 @@
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
       <c r="L7" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="11"/>
@@ -2007,20 +1995,20 @@
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M8" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O8" s="13"/>
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
       <c r="R8" s="13"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="11"/>
@@ -2028,63 +2016,53 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
       <c r="R9" s="13"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="11"/>
       <c r="H10" s="12"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
-      <c r="L10" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="M10" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="N10" s="13" t="s">
-        <v>94</v>
-      </c>
+      <c r="L10" s="13"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="13"/>
       <c r="O10" s="13"/>
-      <c r="P10" s="13" t="s">
-        <v>27</v>
-      </c>
+      <c r="P10" s="13"/>
       <c r="Q10" s="13"/>
-      <c r="R10" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="R10" s="13"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
       <c r="G11" s="11"/>
       <c r="H11" s="12"/>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="L12" s="16"/>
       <c r="M12" s="17"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D13" s="18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
       <c r="J13" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="13"/>
@@ -2095,122 +2073,122 @@
       <c r="Q13" s="13"/>
       <c r="R13" s="13"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="E14" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="F14" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="G14" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="H14" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="J14" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>10</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M14" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="O14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="N14" s="7" t="s">
+      <c r="P14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="O14" s="7" t="s">
+      <c r="Q14" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="P14" s="7" t="s">
+      <c r="R14" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="Q14" s="7" t="s">
+    </row>
+    <row r="15" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="R14" s="7" t="s">
+      <c r="C15" s="22" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="15" spans="2:18" ht="22" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="22" t="s">
+      <c r="D15" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="F15" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="G15" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="H15" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="J15" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>19</v>
       </c>
       <c r="L15" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N15" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="O15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="P15" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="O15" s="9" t="s">
+      <c r="Q15" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="P15" s="9" t="s">
+      <c r="R15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Q15" s="9" t="s">
+    </row>
+    <row r="16" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="23" t="s">
         <v>58</v>
-      </c>
-      <c r="R15" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="23" t="s">
-        <v>60</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G16" s="24"/>
       <c r="H16" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K16" s="25"/>
       <c r="L16" s="25"/>
@@ -2221,15 +2199,15 @@
       <c r="Q16" s="25"/>
       <c r="R16" s="25"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
@@ -2240,34 +2218,34 @@
         <v>50</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K17" s="13"/>
       <c r="L17" s="13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
       <c r="R17" s="13"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -2280,30 +2258,30 @@
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
       <c r="L18" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M18" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
       <c r="R18" s="13"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E19" s="28">
         <v>0.25</v>
@@ -2317,24 +2295,24 @@
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
       <c r="L19" s="13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E20" s="28">
         <v>0.25</v>
@@ -2345,24 +2323,24 @@
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
       <c r="L20" s="13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O20" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E21" s="28">
         <v>0.25</v>
@@ -2373,24 +2351,24 @@
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="O21" s="13" t="s">
         <v>91</v>
-      </c>
-      <c r="M21" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="N21" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="O21" s="13" t="s">
-        <v>95</v>
       </c>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E22" s="28">
         <v>0.25</v>
@@ -2400,33 +2378,23 @@
       <c r="H22" s="12"/>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
-      <c r="L22" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="M22" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="O22" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="P22" s="13" t="s">
-        <v>27</v>
-      </c>
+      <c r="L22" s="13"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -2438,15 +2406,15 @@
       </c>
       <c r="M23" s="15"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
@@ -2458,29 +2426,16 @@
       </c>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" t="s">
-        <v>80</v>
-      </c>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
-      <c r="G25" s="26">
-        <v>1</v>
-      </c>
-      <c r="H25" s="27">
-        <v>50</v>
-      </c>
+      <c r="G25" s="26"/>
+      <c r="H25" s="27"/>
       <c r="J25" s="16"/>
       <c r="K25" s="16"/>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="11"/>
@@ -2489,7 +2444,7 @@
       <c r="K26" s="16"/>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="11"/>
@@ -2498,7 +2453,7 @@
       <c r="K27" s="16"/>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="11"/>
@@ -2507,10 +2462,10 @@
       <c r="K28" s="16"/>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="29"/>
       <c r="C29" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="10"/>
@@ -2519,10 +2474,10 @@
       <c r="H29" s="12"/>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="31"/>
       <c r="C30" s="30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D30" s="16"/>
       <c r="E30" s="10"/>
@@ -2530,7 +2485,7 @@
       <c r="G30" s="11"/>
       <c r="H30" s="12"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="16"/>
       <c r="D31" s="16"/>
       <c r="E31" s="32"/>
@@ -2538,7 +2493,7 @@
       <c r="G31" s="11"/>
       <c r="H31" s="12"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="32"/>
@@ -2546,7 +2501,7 @@
       <c r="G32" s="11"/>
       <c r="H32" s="12"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="16"/>
       <c r="D33" s="16"/>
       <c r="E33" s="32"/>
@@ -2554,7 +2509,7 @@
       <c r="G33" s="11"/>
       <c r="H33" s="12"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="16"/>
       <c r="D34" s="16"/>
       <c r="E34" s="32"/>
@@ -2562,7 +2517,7 @@
       <c r="G34" s="11"/>
       <c r="H34" s="12"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="10"/>
@@ -2570,7 +2525,7 @@
       <c r="G35" s="11"/>
       <c r="H35" s="12"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="10"/>
